--- a/scholarship_application_forms/018_ivy_and_roses_community_fund_scholarship_application--scholarship_application_forms.xlsx
+++ b/scholarship_application_forms/018_ivy_and_roses_community_fund_scholarship_application--scholarship_application_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Scholarship Committees</t>
+          <t>Scholarship Committees Select</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Academic Programs</t>
+          <t>Academic Programs Select</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Financial Info</t>
+          <t>Financial Info Select</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,7 +796,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>employment_history</t>
+          <t>employment_history_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>education_history</t>
+          <t>education_history_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>scholarship_committees_select</t>
+          <t>scholarship_committees_select_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Scholarship Committees</t>
+          <t>Scholarship Committees Select 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>scholarship_info</t>
+          <t>scholarship_info_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Scholarship Info</t>
+          <t>Scholarship Info 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,7 +888,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>academic_programs</t>
+          <t>academic_programs_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>financial_info</t>
+          <t>financial_info_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>employment_history</t>
+          <t>employment_history_3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>education_history</t>
+          <t>education_history_3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>personal_info</t>
+          <t>personal_info_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>contact_info</t>
+          <t>contact_info_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1032,7 +1032,7 @@
   <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="39" customWidth="1" min="1" max="1"/>
+    <col width="41" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1159,7 +1159,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>employment_history_choices</t>
+          <t>employment_history_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1176,7 +1176,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>employment_history_choices</t>
+          <t>employment_history_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1193,7 +1193,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>education_history_choices</t>
+          <t>education_history_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1210,7 +1210,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>education_history_choices</t>
+          <t>education_history_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1227,7 +1227,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>scholarship_committees_select_choices</t>
+          <t>scholarship_committees_select_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1244,7 +1244,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>scholarship_committees_select_choices</t>
+          <t>scholarship_committees_select_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1261,7 +1261,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>academic_programs_choices</t>
+          <t>academic_programs_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1278,7 +1278,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>academic_programs_choices</t>
+          <t>academic_programs_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1295,7 +1295,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>employment_history_choices</t>
+          <t>employment_history_3_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1312,7 +1312,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>employment_history_choices</t>
+          <t>employment_history_3_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1329,7 +1329,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>education_history_choices</t>
+          <t>education_history_3_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1346,7 +1346,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>education_history_choices</t>
+          <t>education_history_3_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
